--- a/supplements/barcelona_samples_2015_2023_joined_results.xlsx
+++ b/supplements/barcelona_samples_2015_2023_joined_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -124,127 +124,130 @@
     <t xml:space="preserve">D2_C2</t>
   </si>
   <si>
+    <t xml:space="preserve">tract_0030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D2_C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3_C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3_C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3_C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMOVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONCI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0027</t>
+  </si>
+  <si>
     <t xml:space="preserve">tract_0028</t>
   </si>
   <si>
-    <t xml:space="preserve">tract_0030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2_C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3_C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3_C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0045</t>
+    <t xml:space="preserve">tract_0029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tract_0042</t>
   </si>
   <si>
     <t xml:space="preserve">tract_0046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3_C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REMOVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NONCI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tract_0040</t>
   </si>
   <si>
     <t xml:space="preserve">tract_0048</t>
@@ -868,19 +871,19 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -889,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -907,7 +910,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -916,19 +919,19 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -937,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="str">
         <f>IF(AND(NOT(ISBLANK(L9)),NOT(ISBLANK(M9))),1,"")</f>
@@ -952,38 +955,22 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
       <c r="K10" t="b">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
+      <c r="L10"/>
+      <c r="M10"/>
       <c r="N10" t="str">
         <f>IF(AND(NOT(ISBLANK(L10)),NOT(ISBLANK(M10))),1,"")</f>
       </c>
@@ -1042,22 +1029,38 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
       </c>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
-      <c r="L12"/>
-      <c r="M12"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
       <c r="N12" t="str">
         <f>IF(AND(NOT(ISBLANK(L12)),NOT(ISBLANK(M12))),1,"")</f>
       </c>
@@ -1071,7 +1074,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -1080,19 +1083,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -1101,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="str">
         <f>IF(AND(NOT(ISBLANK(L13)),NOT(ISBLANK(M13))),1,"")</f>
@@ -1116,7 +1119,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -1125,19 +1128,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1146,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="str">
         <f>IF(AND(NOT(ISBLANK(L14)),NOT(ISBLANK(M14))),1,"")</f>
@@ -1161,10 +1164,10 @@
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -1206,10 +1209,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1251,7 +1254,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -1296,38 +1299,30 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F18"/>
       <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H18"/>
       <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18"/>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M18"/>
       <c r="N18" t="str">
         <f>IF(AND(NOT(ISBLANK(L18)),NOT(ISBLANK(M18))),1,"")</f>
       </c>
@@ -1341,7 +1336,7 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
@@ -1386,7 +1381,7 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
@@ -1431,25 +1426,25 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1458,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1476,28 +1471,28 @@
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -1506,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="str">
         <f>IF(AND(NOT(ISBLANK(L22)),NOT(ISBLANK(M22))),1,"")</f>
@@ -1521,28 +1516,28 @@
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -1551,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="str">
         <f>IF(AND(NOT(ISBLANK(L23)),NOT(ISBLANK(M23))),1,"")</f>
@@ -1566,28 +1561,28 @@
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -1596,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="str">
         <f>IF(AND(NOT(ISBLANK(L24)),NOT(ISBLANK(M24))),1,"")</f>
@@ -1611,7 +1606,7 @@
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
         <v>35</v>
@@ -1656,7 +1651,7 @@
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
         <v>35</v>
@@ -1701,22 +1696,38 @@
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
+        <v>38</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
-      <c r="L27"/>
-      <c r="M27"/>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
       <c r="N27" t="str">
         <f>IF(AND(NOT(ISBLANK(L27)),NOT(ISBLANK(M27))),1,"")</f>
       </c>
@@ -1730,10 +1741,10 @@
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -1775,38 +1786,22 @@
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
       <c r="K29" t="b">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
+      <c r="L29"/>
+      <c r="M29"/>
       <c r="N29" t="str">
         <f>IF(AND(NOT(ISBLANK(L29)),NOT(ISBLANK(M29))),1,"")</f>
       </c>
@@ -1820,28 +1815,28 @@
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -1850,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="str">
         <f>IF(AND(NOT(ISBLANK(L30)),NOT(ISBLANK(M30))),1,"")</f>
@@ -1865,10 +1860,10 @@
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1910,10 +1905,10 @@
         <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1955,10 +1950,10 @@
         <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E33"/>
       <c r="F33"/>
@@ -1984,10 +1979,10 @@
         <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -2029,28 +2024,28 @@
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2059,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="str">
         <f>IF(AND(NOT(ISBLANK(L35)),NOT(ISBLANK(M35))),1,"")</f>
@@ -2074,10 +2069,10 @@
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -2119,25 +2114,25 @@
         <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2146,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2164,25 +2159,25 @@
         <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2191,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2209,38 +2204,22 @@
         <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
       <c r="K39" t="b">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
+      <c r="L39"/>
+      <c r="M39"/>
       <c r="N39" t="str">
         <f>IF(AND(NOT(ISBLANK(L39)),NOT(ISBLANK(M39))),1,"")</f>
       </c>
@@ -2254,22 +2233,38 @@
         <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
+        <v>48</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
-      <c r="L40"/>
-      <c r="M40"/>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" t="str">
         <f>IF(AND(NOT(ISBLANK(L40)),NOT(ISBLANK(M40))),1,"")</f>
       </c>
@@ -2283,25 +2278,25 @@
         <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2310,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2321,409 +2316,25 @@
       <c r="O41"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" t="s">
-        <v>45</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
       <c r="K42" t="b">
         <v>0</v>
       </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
+      <c r="L42"/>
+      <c r="M42"/>
       <c r="N42" t="str">
         <f>IF(AND(NOT(ISBLANK(L42)),NOT(ISBLANK(M42))),1,"")</f>
       </c>
       <c r="O42"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" t="str">
-        <f>IF(AND(NOT(ISBLANK(L43)),NOT(ISBLANK(M43))),1,"")</f>
-      </c>
-      <c r="O43"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" t="s">
-        <v>45</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="str">
-        <f>IF(AND(NOT(ISBLANK(L44)),NOT(ISBLANK(M44))),1,"")</f>
-      </c>
-      <c r="O44"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="str">
-        <f>IF(AND(NOT(ISBLANK(L45)),NOT(ISBLANK(M45))),1,"")</f>
-      </c>
-      <c r="O45"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="str">
-        <f>IF(AND(NOT(ISBLANK(L46)),NOT(ISBLANK(M46))),1,"")</f>
-      </c>
-      <c r="O46"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" t="s">
-        <v>51</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="str">
-        <f>IF(AND(NOT(ISBLANK(L47)),NOT(ISBLANK(M47))),1,"")</f>
-      </c>
-      <c r="O47"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="str">
-        <f>IF(AND(NOT(ISBLANK(L48)),NOT(ISBLANK(M48))),1,"")</f>
-      </c>
-      <c r="O48"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="str">
-        <f>IF(AND(NOT(ISBLANK(L49)),NOT(ISBLANK(M49))),1,"")</f>
-      </c>
-      <c r="O49"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" t="s">
-        <v>51</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="str">
-        <f>IF(AND(NOT(ISBLANK(L50)),NOT(ISBLANK(M50))),1,"")</f>
-      </c>
-      <c r="O50"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2788,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -2833,40 +2444,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="str">
         <f>IF(AND(NOT(ISBLANK(L4)),NOT(ISBLANK(M4))),1,"")</f>
@@ -2878,13 +2489,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2923,31 +2534,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -2956,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="str">
         <f>IF(AND(NOT(ISBLANK(L6)),NOT(ISBLANK(M6))),1,"")</f>
@@ -2968,40 +2579,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="str">
         <f>IF(AND(NOT(ISBLANK(L7)),NOT(ISBLANK(M7))),1,"")</f>
@@ -3013,31 +2624,31 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -3046,86 +2657,12 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="str">
         <f>IF(AND(NOT(ISBLANK(L8)),NOT(ISBLANK(M8))),1,"")</f>
       </c>
       <c r="O8"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9" t="str">
-        <f>IF(AND(NOT(ISBLANK(L9)),NOT(ISBLANK(M9))),1,"")</f>
-      </c>
-      <c r="O9"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="str">
-        <f>IF(AND(NOT(ISBLANK(L10)),NOT(ISBLANK(M10))),1,"")</f>
-      </c>
-      <c r="O10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3190,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -3235,10 +2772,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -3280,7 +2817,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -3288,17 +2825,33 @@
       <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
-      <c r="L5"/>
-      <c r="M5"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" t="str">
         <f>IF(AND(NOT(ISBLANK(L5)),NOT(ISBLANK(M5))),1,"")</f>
       </c>
@@ -3309,7 +2862,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -3318,19 +2871,19 @@
         <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3339,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -3354,10 +2907,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -3399,7 +2952,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -3444,7 +2997,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -3489,25 +3042,41 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
         <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
-      <c r="L10"/>
-      <c r="M10"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" t="str">
         <f>IF(AND(NOT(ISBLANK(L10)),NOT(ISBLANK(M10))),1,"")</f>
       </c>
@@ -3518,7 +3087,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
@@ -3527,16 +3096,24 @@
         <v>22</v>
       </c>
       <c r="E11"/>
-      <c r="F11"/>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
       <c r="G11"/>
-      <c r="H11"/>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
       <c r="I11"/>
-      <c r="J11"/>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11"/>
-      <c r="M11"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" t="str">
         <f>IF(AND(NOT(ISBLANK(L11)),NOT(ISBLANK(M11))),1,"")</f>
       </c>
@@ -3547,7 +3124,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
@@ -3592,7 +3169,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
         <v>25</v>
@@ -3637,7 +3214,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -3682,7 +3259,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -3727,10 +3304,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -3772,10 +3349,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
@@ -3817,10 +3394,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
@@ -3862,7 +3439,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
@@ -3907,10 +3484,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -3952,10 +3529,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -3997,10 +3574,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -4042,10 +3619,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -4087,7 +3664,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
@@ -4096,31 +3673,31 @@
         <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="str">
         <f>IF(AND(NOT(ISBLANK(L24)),NOT(ISBLANK(M24))),1,"")</f>
@@ -4132,7 +3709,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -4177,7 +3754,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
         <v>34</v>
@@ -4222,10 +3799,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
         <v>35</v>
@@ -4267,10 +3844,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
         <v>35</v>
@@ -4312,10 +3889,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
         <v>35</v>
@@ -4357,10 +3934,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
         <v>35</v>
@@ -4402,10 +3979,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
         <v>35</v>
@@ -4447,13 +4024,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" t="s">
         <v>38</v>
-      </c>
-      <c r="D32" t="s">
-        <v>39</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -4492,13 +4069,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -4537,13 +4114,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -4582,13 +4159,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -4627,25 +4204,41 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
+        <v>38</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
       <c r="K36" t="b">
         <v>0</v>
       </c>
-      <c r="L36"/>
-      <c r="M36"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" t="str">
         <f>IF(AND(NOT(ISBLANK(L36)),NOT(ISBLANK(M36))),1,"")</f>
       </c>
@@ -4656,13 +4249,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -4701,13 +4294,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -4746,13 +4339,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -4791,13 +4384,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -4836,13 +4429,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" t="s">
         <v>42</v>
-      </c>
-      <c r="D41" t="s">
-        <v>43</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -4881,13 +4474,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -4926,13 +4519,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -4971,13 +4564,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -5016,13 +4609,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -5061,13 +4654,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
         <v>77</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -5106,13 +4699,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -5151,13 +4744,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -5196,13 +4789,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -5241,13 +4834,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -5286,13 +4879,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
         <v>79</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -5325,6 +4918,51 @@
         <f>IF(AND(NOT(ISBLANK(L51)),NOT(ISBLANK(M51))),1,"")</f>
       </c>
       <c r="O51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="str">
+        <f>IF(AND(NOT(ISBLANK(L52)),NOT(ISBLANK(M52))),1,"")</f>
+      </c>
+      <c r="O52"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
